--- a/hira_material_automation/output/monthly/202601_202606__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:24:21</t>
+          <t>2026-06-14T22:17:38</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5e8cb8cb8051b87b31e32db2380fd3dc13ba2e71bfc1a654dd25a45d3235abe5</t>
+          <t>1c325bd034243e9ebb41d135b8be2738a33f9f12bc4f7de892f93069c13ab567</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:38</t>
+          <t>2026-06-24T22:22:25</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1c325bd034243e9ebb41d135b8be2738a33f9f12bc4f7de892f93069c13ab567</t>
+          <t>7b069dcca2f168081c577e5d80b03c2fc6ee841625b527c50dafdfaed8991349</t>
         </is>
       </c>
     </row>
